--- a/processed_ruby_restored_xlsx/sc122_瑠璃千代２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc122_瑠璃千代２：恋人化.ss.xlsx
@@ -728,8 +728,8 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>She was probably checking the snacks she's hiding, but
-the way she moves makes it obvious.</t>
+          <t>She was probably checking the snacks she's hiding,
+but the way she moves makes it obvious.</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -775,8 +775,8 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, who doesn't know Rin-chan has snacks, gives
-a perfectly reasonable opinion.</t>
+          <t>Nono-chan, who doesn't know Rin-chan has snacks,
+gives a perfectly reasonable opinion.</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -991,7 +991,8 @@
       <c r="B35" s="1" t="inlineStr">
         <is>
           <t>Rin-chan looked for a moment like she’d been caught,
-then quickly put on an awkward face and hid the snack.</t>
+then quickly put on an awkward face and hid the
+snack.</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1098,8 +1099,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>At the time we were all lovey-dovey in the bath and it
-felt amazing, but as time passes the embarrassment
+          <t>At the time we were all lovey-dovey in the bath and
+it felt amazing, but as time passes the embarrassment
 comes creeping back.</t>
         </is>
       </c>
@@ -1131,8 +1132,8 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>I feel both relieved and a little lonely… it's a weird
-feeling.</t>
+          <t>I feel both relieved and a little lonely… it's a
+weird feeling.</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1686,8 +1687,8 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>There's no real reason to worry, but for some reason I
-can't stop thinking about her.</t>
+          <t>There's no real reason to worry, but for some reason
+I can't stop thinking about her.</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1762,8 +1763,8 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>When I knocked and called out, the same unchanged tone
-came back.</t>
+          <t>When I knocked and called out, the same unchanged
+tone came back.</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1901,8 +1902,8 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>The gesture looks like her usual Rurichiyo-chan style,
-but it's actually a bit different.</t>
+          <t>The gesture looks like her usual Rurichiyo-chan
+style, but it's actually a bit different.</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2007,8 +2008,8 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>I said it just to bait her, and Rurichiyo-chan widened
-her eyes and murmured.</t>
+          <t>I said it just to bait her, and Rurichiyo-chan
+widened her eyes and murmured.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2068,8 +2069,8 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan kept up a cheerful smile, but there was
-a shadow in her tone.</t>
+          <t>Rurichiyo-chan kept up a cheerful smile, but there
+was a shadow in her tone.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2221,8 +2222,8 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>「I've known Rurichiyo-chan since she was much smaller,
-so I'm sure I can be of help！」</t>
+          <t>「I've known Rurichiyo-chan since she was much
+smaller, so I'm sure I can be of help！」</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2803,8 +2804,8 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>But because she's so close, she's also distant when it
-comes to taking a step forward...</t>
+          <t>But because she's so close, she's also distant when
+it comes to taking a step forward...</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2896,8 +2897,8 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan forces a cheerful face, but a wry smile
-still slips out.</t>
+          <t>Rurichiyo-chan forces a cheerful face, but a wry
+smile still slips out.</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3141,8 +3142,8 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>...A day passed with me and Rurichiyo-chan still stuck
-in that slightly awkward relationship.</t>
+          <t>...A day passed with me and Rurichiyo-chan still
+stuck in that slightly awkward relationship.</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3157,7 +3158,8 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>That said, Rurichiyo-chan doesn't show any sign of it.</t>
+          <t>That said, Rurichiyo-chan doesn't show any sign of
+it.</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3432,8 +3434,8 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>But it's Rin-chan's usual energy, so I'm sorry, but it
-doesn't really look like her.</t>
+          <t>But it's Rin-chan's usual energy, so I'm sorry, but
+it doesn't really look like her.</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3851,8 +3853,8 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... When Janitor-sensei says that, I'm starting to
-feel like something's off, you know？」</t>
+          <t>「Hmm... When Janitor-sensei says that, I'm starting
+to feel like something's off, you know？」</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -4065,8 +4067,8 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan teased Rurichiyo-chan for covering it up, and
-Miru-chan, getting drawn in, flew into a rage.</t>
+          <t>Rin-chan teased Rurichiyo-chan for covering it up,
+and Miru-chan, getting drawn in, flew into a rage.</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4232,8 +4234,8 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>But I still feel like the knot in my chest hasn't gone
-away.</t>
+          <t>But I still feel like the knot in my chest hasn't
+gone away.</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4278,8 +4280,8 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>Some awkward thoughts popped into my head, and I stood
-up as if to run away.</t>
+          <t>Some awkward thoughts popped into my head, and I
+stood up as if to run away.</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4552,8 +4554,8 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>When the door opens, a gust of wind rushes past me and
-darts away.</t>
+          <t>When the door opens, a gust of wind rushes past me
+and darts away.</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4842,7 +4844,8 @@
       <c r="B286" s="1" t="inlineStr">
         <is>
           <t>Nono-chan, caught off guard by the suddenness of it
-all, was so stunned she didn’t know what had happened.</t>
+all, was so stunned she didn’t know what had
+happened.</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -5241,8 +5244,8 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>「See, see... if we don't meet face-to-face, it doesn't
-feel like we've really met...！」</t>
+          <t>「See, see... if we don't meet face-to-face, it
+doesn't feel like we've really met...！」</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -6672,8 +6675,8 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo-baa-chan said, nodding with a self-satisfied
-look.</t>
+          <t>Kikuchiyo-baa-chan said, nodding with a
+self-satisfied look.</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -7069,8 +7072,8 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>「Of course she is. I'm so fond of her I could just eat
-her up......but it can't be only that, can it？」</t>
+          <t>「Of course she is. I'm so fond of her I could just
+eat her up......but it can't be only that, can it？」</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -7286,8 +7289,8 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>As always, Kikuchiyo-baa-chan had that self-satisfied,
-knowing look.</t>
+          <t>As always, Kikuchiyo-baa-chan had that
+self-satisfied, knowing look.</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7378,8 +7381,8 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t>Hearing that with a blank expression only increased my
-confusion.</t>
+          <t>Hearing that with a blank expression only increased
+my confusion.</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -7562,9 +7565,9 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>Startled and straightening up instinctively under that
-piercing stare, Kikuchiyo-baa-chan folded her arms and
-narrowed her eyes even more.</t>
+          <t>Startled and straightening up instinctively under
+that piercing stare, Kikuchiyo-baa-chan folded her
+arms and narrowed her eyes even more.</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7594,8 +7597,9 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>「No — I'm not just any old broad！ I'm an old broad who
-loves Rurichiyo deeply, deeeply！ Just an old broad！」</t>
+          <t>「No — I'm not just any old broad！ I'm an old broad
+who loves Rurichiyo deeply, deeeply！ Just an old
+broad！」</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -8042,8 +8046,8 @@
       <c r="B494" s="1" t="inlineStr">
         <is>
           <t>「Well, mind you, it's gonna turn into a girls' talk
-between the girls, so you won't have any chance to get
-in, y'know！」</t>
+between the girls, so you won't have any chance to
+get in, y'know！」</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -8367,8 +8371,8 @@
       <c r="B515" s="1" t="inlineStr">
         <is>
           <t>Kikuchiyo-baa-chan gets home just after eight, and
-everyone’s probably finished bathing and getting ready
-for bed by now.</t>
+everyone’s probably finished bathing and getting
+ready for bed by now.</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -8474,8 +8478,8 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>I-It's not like Kikuchiyo-baa-chan told me to do it or
-anything, it's because I need to wash it tomorrow.</t>
+          <t>I-It's not like Kikuchiyo-baa-chan told me to do it
+or anything, it's because I need to wash it tomorrow.</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8520,8 +8524,8 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>I take a deep, steady breath to calm myself, then pick
-up each piece of clothing everyone has tossed
+          <t>I take a deep, steady breath to calm myself, then
+pick up each piece of clothing everyone has tossed
 everywhere and fold them one by one.</t>
         </is>
       </c>
@@ -8768,7 +8772,8 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>So Rurichiyo-chan can be absent-minded sometimes, huh.</t>
+          <t>So Rurichiyo-chan can be absent-minded sometimes,
+huh.</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -9458,8 +9463,9 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>When I gave up and apologized honestly, Rurichiyo-chan
-covered her mouth with her hand and collapsed.</t>
+          <t>When I gave up and apologized honestly,
+Rurichiyo-chan covered her mouth with her hand and
+collapsed.</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -9839,8 +9845,8 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>「No, no！ But hey, I was just folding the clothes I was
-going to wash tomorrow, and I didn't have any bad
+          <t>「No, no！ But hey, I was just folding the clothes I
+was going to wash tomorrow, and I didn't have any bad
 intentions from the start！」</t>
         </is>
       </c>
@@ -9931,8 +9937,8 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>With the circumstantial evidence stacked against me, I
-wasn't even allowed to struggle.</t>
+          <t>With the circumstantial evidence stacked against me,
+I wasn't even allowed to struggle.</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -9977,8 +9983,8 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>Even if I couldn't make excuses, I tried to hang on by
-subtly shifting the point.</t>
+          <t>Even if I couldn't make excuses, I tried to hang on
+by subtly shifting the point.</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -10008,8 +10014,8 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>「You didn't think I'd be a criminal just because I was
-sniffing panties... right？」</t>
+          <t>「You didn't think I'd be a criminal just because I
+was sniffing panties... right？」</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -10100,8 +10106,8 @@
       </c>
       <c r="B628" s="1" t="inlineStr">
         <is>
-          <t>「Great-aunt said. If Oji-sama was sniffing panties, be
-careful...」</t>
+          <t>「Great-aunt said. If Oji-sama was sniffing panties,
+be careful...」</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -10300,7 +10306,8 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>As expected of the Arisugawa family head, even if old.</t>
+          <t>As expected of the Arisugawa family head, even if
+old.</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10315,8 +10322,8 @@
       </c>
       <c r="B642" s="1" t="inlineStr">
         <is>
-          <t>Her observational eye, honed beyond worldly tricks and
-gambits, was unclouded.</t>
+          <t>Her observational eye, honed beyond worldly tricks
+and gambits, was unclouded.</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -10361,8 +10368,8 @@
       </c>
       <c r="B645" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama... we shouldn't be doing naughty things with
-grown men, you know？」</t>
+          <t>「Oji-sama... we shouldn't be doing naughty things
+with grown men, you know？」</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -10422,7 +10429,8 @@
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>If I said anything, she'd just keep repeating herself.</t>
+          <t>If I said anything, she'd just keep repeating
+herself.</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -10484,8 +10492,8 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>Even Kikuchiyo-baa-chan said that Rurichiyo-chan loves
-me, like, suuuper much...</t>
+          <t>Even Kikuchiyo-baa-chan said that Rurichiyo-chan
+loves me, like, suuuper much...</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -10590,8 +10598,8 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>「Ah, at least it's my panties, and you're not sniffing
-other girls' panties... right...？」</t>
+          <t>「Ah, at least it's my panties, and you're not
+sniffing other girls' panties... right...？」</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -10638,7 +10646,8 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>When I thought that, I nodded inside at the same time.</t>
+          <t>When I thought that, I nodded inside at the same
+time.</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -11831,8 +11840,9 @@
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>But Rurichiyo-chan answered without hesitation and, in
-a slow, lumbering way, began taking off her clothes.</t>
+          <t>But Rurichiyo-chan answered without hesitation and,
+in a slow, lumbering way, began taking off her
+clothes.</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -11847,8 +11857,8 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>You can tell she’s not completely over it, but even so
-she takes off her clothes one by one and ends up
+          <t>You can tell she’s not completely over it, but even
+so she takes off her clothes one by one and ends up
 completely naked.</t>
         </is>
       </c>
@@ -11955,8 +11965,8 @@
       </c>
       <c r="B749" s="1" t="inlineStr">
         <is>
-          <t>I'd decided in my heart to stop partway, but there was
-naked Rurichiyo-chan right in front of me.</t>
+          <t>I'd decided in my heart to stop partway, but there
+was naked Rurichiyo-chan right in front of me.</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -12322,9 +12332,9 @@
       </c>
       <c r="B773" s="1" t="inlineStr">
         <is>
-          <t>I planned to make her give up with a harsh word rather
-than be clumsy and gentle, but there was no way I
-could say something like that.</t>
+          <t>I planned to make her give up with a harsh word
+rather than be clumsy and gentle, but there was no
+way I could say something like that.</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -12478,7 +12488,8 @@
       <c r="B783" s="1" t="inlineStr">
         <is>
           <t>When I press the tip of my penis against the soft
-flesh of the mound, anticipation wells up in my chest.</t>
+flesh of the mound, anticipation wells up in my
+chest.</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -12660,8 +12671,8 @@
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>I grip my penis firmly, check the position between her
-legs, and try inserting again.</t>
+          <t>I grip my penis firmly, check the position between
+her legs, and try inserting again.</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -12751,8 +12762,8 @@
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan squeezes her eyes shut... and more than
-that, she's curling her body up tight.</t>
+          <t>Rurichiyo-chan squeezes her eyes shut... and more
+than that, she's curling her body up tight.</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -12842,7 +12853,8 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>Seems like she's really freaking out inside after all.</t>
+          <t>Seems like she's really freaking out inside after
+all.</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -12857,8 +12869,8 @@
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>Taking Rurichiyo-chan's first time in this state would
-make me a real monster...</t>
+          <t>Taking Rurichiyo-chan's first time in this state
+would make me a real monster...</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -13149,8 +13161,8 @@
       <c r="B827" s="1" t="inlineStr">
         <is>
           <t>Because I knew Rurichiyo-chan would act tough, I
-caught her off guard and gave her a light flick on the
-forehead.</t>
+caught her off guard and gave her a light flick on
+the forehead.</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -13593,8 +13605,8 @@
       </c>
       <c r="B856" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan said nothing and just looked at me with
-an embarrassed little smile.</t>
+          <t>Rurichiyo-chan said nothing and just looked at me
+with an embarrassed little smile.</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -13793,8 +13805,8 @@
       </c>
       <c r="B869" s="1" t="inlineStr">
         <is>
-          <t>「What should we do? Shall I use my hands like everyone
-did? Or… like last time, with my mouth…?」</t>
+          <t>「What should we do? Shall I use my hands like
+everyone did? Or… like last time, with my mouth…?」</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -13871,8 +13883,8 @@
       </c>
       <c r="B874" s="1" t="inlineStr">
         <is>
-          <t>With less guilt to deal with, my excitement just comes
-rushing back.</t>
+          <t>With less guilt to deal with, my excitement just
+comes rushing back.</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -13948,8 +13960,8 @@
       </c>
       <c r="B879" s="1" t="inlineStr">
         <is>
-          <t>「Understood... Then I will suppress Oji-sama's passion
-with my hand！」</t>
+          <t>「Understood... Then I will suppress Oji-sama's
+passion with my hand！」</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -13979,8 +13991,8 @@
       </c>
       <c r="B881" s="1" t="inlineStr">
         <is>
-          <t>「Uh... yeah... but I think passion isn't something you
-should suppress — it's something you let out.」</t>
+          <t>「Uh... yeah... but I think passion isn't something
+you should suppress — it's something you let out.」</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -14026,7 +14038,8 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>「Pardon？ Passion isn't something to be suppressed...？」</t>
+          <t>「Pardon？ Passion isn't something to be
+suppressed...？」</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -14287,8 +14300,8 @@
       </c>
       <c r="B901" s="1" t="inlineStr">
         <is>
-          <t>Feeling a little calmer again, I flung myself onto the
-bed.</t>
+          <t>Feeling a little calmer again, I flung myself onto
+the bed.</t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -14440,8 +14453,8 @@
       </c>
       <c r="B911" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan sat up groggily, got down on all fours,
-and peered at my face.</t>
+          <t>Rurichiyo-chan sat up groggily, got down on all
+fours, and peered at my face.</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -14654,8 +14667,8 @@
       </c>
       <c r="B925" s="1" t="inlineStr">
         <is>
-          <t>As if seeing right through that, Rurichiyo-chan's hand
-reached for the penis.</t>
+          <t>As if seeing right through that, Rurichiyo-chan's
+hand reached for the penis.</t>
         </is>
       </c>
       <c r="C925" t="n">
@@ -14700,8 +14713,8 @@
       </c>
       <c r="B928" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, noticing my twitching penis, scolds me
-with a puzzled look.</t>
+          <t>Rurichiyo-chan, noticing my twitching penis, scolds
+me with a puzzled look.</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -15008,8 +15021,8 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！ Mm... hehe, you twitch every time I kiss you,
-don't you？」</t>
+          <t>「Smooch！ Mm... hehe, you twitch every time I kiss
+you, don't you？」</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -15224,7 +15237,8 @@
       </c>
       <c r="B962" s="1" t="inlineStr">
         <is>
-          <t>「Ah... is that so...！ This feels... good, doesn't it？」</t>
+          <t>「Ah... is that so...！ This feels... good, doesn't
+it？」</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -15684,7 +15698,8 @@
       </c>
       <c r="B992" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan begins to take my open mouth into hers.</t>
+          <t>Rurichiyo-chan begins to take my open mouth into
+hers.</t>
         </is>
       </c>
       <c r="C992" t="n">
@@ -15899,8 +15914,8 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>...That's right. On Nono-chan's very first night here,
-we practiced ejaculating in the bath.</t>
+          <t>...That's right. On Nono-chan's very first night
+here, we practiced ejaculating in the bath.</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -15915,8 +15930,8 @@
       </c>
       <c r="B1007" s="1" t="inlineStr">
         <is>
-          <t>At that time, Rurichiyo-chan wouldn't give up her turn
-to anyone.</t>
+          <t>At that time, Rurichiyo-chan wouldn't give up her
+turn to anyone.</t>
         </is>
       </c>
       <c r="C1007" t="n">
@@ -15946,8 +15961,8 @@
       </c>
       <c r="B1009" s="1" t="inlineStr">
         <is>
-          <t>「You don't have to overthink it, okay？ Just move it up
-and down, kinda 'shiko-shiko.'」</t>
+          <t>「You don't have to overthink it, okay？ Just move it
+up and down, kinda 'shiko-shiko.'」</t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -16225,8 +16240,8 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ahh！ It's that fluid that comes out when it feels
-good, isn't it...！？」</t>
+          <t>「Ah, ahh！ It's that fluid that comes out when it
+feels good, isn't it...！？」</t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -16332,8 +16347,8 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>The realization that I'm making me feel good is egging
-Rurichiyo-chan on……。</t>
+          <t>The realization that I'm making me feel good is
+egging Rurichiyo-chan on……。</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -16363,7 +16378,8 @@
       </c>
       <c r="B1036" s="1" t="inlineStr">
         <is>
-          <t>「Ohah…… Oji-sama, you have such a cute face…… mm—chu！」</t>
+          <t>「Ohah…… Oji-sama, you have such a cute face……
+mm—chu！」</t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -16408,8 +16424,8 @@
       </c>
       <c r="B1039" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, getting a bit carried away, gives me a
-smooch with her usual graceful, gentle smile.</t>
+          <t>Rurichiyo-chan, getting a bit carried away, gives me
+a smooch with her usual graceful, gentle smile.</t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -16669,8 +16685,8 @@
       </c>
       <c r="B1056" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, now completely cheerful, starts giving
-a kiss while beginning a handjob.</t>
+          <t>Rurichiyo-chan, now completely cheerful, starts
+giving a kiss while beginning a handjob.</t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -16778,8 +16794,9 @@
       </c>
       <c r="B1063" s="1" t="inlineStr">
         <is>
-          <t>A ticklish kind of pleasure ran through my whole body,
-and I couldn't help but let out a whimpering sound.</t>
+          <t>A ticklish kind of pleasure ran through my whole
+body, and I couldn't help but let out a whimpering
+sound.</t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -16886,8 +16903,8 @@
       </c>
       <c r="B1070" s="1" t="inlineStr">
         <is>
-          <t>She said it coquettishly, and Rurichiyo-chan smiled as
-she kept going.</t>
+          <t>She said it coquettishly, and Rurichiyo-chan smiled
+as she kept going.</t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -17211,8 +17228,8 @@
       </c>
       <c r="B1091" s="1" t="inlineStr">
         <is>
-          <t>Drunk on embarrassment and pleasure, I twisted my body
-and let out another needy sound.</t>
+          <t>Drunk on embarrassment and pleasure, I twisted my
+body and let out another needy sound.</t>
         </is>
       </c>
       <c r="C1091" t="n">
@@ -17688,8 +17705,8 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>「…Then please, don’t hold back — pyu-pyu, go ahead and
-squirt for me…！」</t>
+          <t>「…Then please, don’t hold back — pyu-pyu, go ahead
+and squirt for me…！」</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -17887,8 +17904,8 @@
       </c>
       <c r="B1135" s="1" t="inlineStr">
         <is>
-          <t>「Chubu, chuba！ N, pu！ Hah, haa...！ Chukk！ Chuku！ Juju！
-Ju！」</t>
+          <t>「Chubu, chuba！ N, pu！ Hah, haa...！ Chukk！ Chuku！
+Juju！ Ju！」</t>
         </is>
       </c>
       <c r="C1135" t="n">
@@ -17933,9 +17950,9 @@
       </c>
       <c r="B1138" s="1" t="inlineStr">
         <is>
-          <t>The arousal from my penis combines with the excitement
-of the kisses, and a current of pleasure runs through
-my body...！</t>
+          <t>The arousal from my penis combines with the
+excitement of the kisses, and a current of pleasure
+runs through my body...！</t>
         </is>
       </c>
       <c r="C1138" t="n">
@@ -18118,8 +18135,8 @@
       </c>
       <c r="B1150" s="1" t="inlineStr">
         <is>
-          <t>Hearing Rurichiyo-chan's words, I focused my attention
-on my lower body.</t>
+          <t>Hearing Rurichiyo-chan's words, I focused my
+attention on my lower body.</t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -18303,7 +18320,8 @@
       </c>
       <c r="B1162" s="1" t="inlineStr">
         <is>
-          <t>「I’m so glad… I was able to make Oji-sama feel good…！」</t>
+          <t>「I’m so glad… I was able to make Oji-sama feel
+good…！」</t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -18561,8 +18579,8 @@
       </c>
       <c r="B1179" s="1" t="inlineStr">
         <is>
-          <t>I hold Rurichiyo-chan’s hand with both of my hands and
-gently wipe off the sticky semen.</t>
+          <t>I hold Rurichiyo-chan’s hand with both of my hands
+and gently wipe off the sticky semen.</t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -18655,7 +18673,8 @@
         <is>
           <t>When she was giving a handjob with a 'chu' sound,
 excitement seemed to win out and she forgot, but
-gradually she cooled off and probably got embarrassed.</t>
+gradually she cooled off and probably got
+embarrassed.</t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -18685,7 +18704,8 @@
       </c>
       <c r="B1187" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu... Oji-sama, has your passion been restrained？」</t>
+          <t>「Ufufu... Oji-sama, has your passion been
+restrained？」</t>
         </is>
       </c>
       <c r="C1187" t="n">
@@ -18868,9 +18888,9 @@
       </c>
       <c r="B1199" s="1" t="inlineStr">
         <is>
-          <t>When I tightened my expression and looked her straight
-in the face, Rurichiyo-chan had a blank, surprised
-look.</t>
+          <t>When I tightened my expression and looked her
+straight in the face, Rurichiyo-chan had a blank,
+surprised look.</t>
         </is>
       </c>
       <c r="C1199" t="n">
@@ -19404,7 +19424,8 @@
       </c>
       <c r="B1234" s="1" t="inlineStr">
         <is>
-          <t>As expected, Rurichiyo-chan raised her voice in anger.</t>
+          <t>As expected, Rurichiyo-chan raised her voice in
+anger.</t>
         </is>
       </c>
       <c r="C1234" t="n">
@@ -19495,8 +19516,8 @@
       </c>
       <c r="B1240" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan nodded dejectedly and began putting her
-clothes on sluggishly.</t>
+          <t>Rurichiyo-chan nodded dejectedly and began putting
+her clothes on sluggishly.</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -19756,8 +19777,8 @@
       </c>
       <c r="B1257" s="1" t="inlineStr">
         <is>
-          <t>And then, moving slowly, she got out of bed and walked
-away.</t>
+          <t>And then, moving slowly, she got out of bed and
+walked away.</t>
         </is>
       </c>
       <c r="C1257" t="n">
@@ -20230,8 +20251,8 @@
       </c>
       <c r="B1288" s="1" t="inlineStr">
         <is>
-          <t>I knew that, but all I could do was quietly watch over
-Rurichiyo-chan.</t>
+          <t>I knew that, but all I could do was quietly watch
+over Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C1288" t="n">
@@ -20447,9 +20468,9 @@
       </c>
       <c r="B1302" s="1" t="inlineStr">
         <is>
-          <t>Because it was a familiar face, she could go up to the
-deck without a boarding ticket, but she can't really
-linger like that.</t>
+          <t>Because it was a familiar face, she could go up to
+the deck without a boarding ticket, but she can't
+really linger like that.</t>
         </is>
       </c>
       <c r="C1302" t="n">
@@ -20829,9 +20850,9 @@
       </c>
       <c r="B1327" s="1" t="inlineStr">
         <is>
-          <t>「Because if the rest of us all go home, Oji-sama would
-be all alone in that big dormitory, right？ I thought
-that would be lonely...！」</t>
+          <t>「Because if the rest of us all go home, Oji-sama
+would be all alone in that big dormitory, right？ I
+thought that would be lonely...！」</t>
         </is>
       </c>
       <c r="C1327" t="n">
@@ -21134,8 +21155,8 @@
       </c>
       <c r="B1347" s="1" t="inlineStr">
         <is>
-          <t>And I got off the ferry as if being led by the hand by
-Rurichiyo-chan.</t>
+          <t>And I got off the ferry as if being led by the hand
+by Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C1347" t="n">
@@ -21413,8 +21434,8 @@
       <c r="B1365" s="1" t="inlineStr">
         <is>
           <t>My sister, unlike me, is capable, so she's busy
-expanding her network without relying on the Arisugawa
-family name.</t>
+expanding her network without relying on the
+Arisugawa family name.</t>
         </is>
       </c>
       <c r="C1365" t="n">
@@ -22141,8 +22162,8 @@
       </c>
       <c r="B1412" s="1" t="inlineStr">
         <is>
-          <t>It went so anticlimactically that I actually felt kind
-of deflated.</t>
+          <t>It went so anticlimactically that I actually felt
+kind of deflated.</t>
         </is>
       </c>
       <c r="C1412" t="n">
@@ -22325,8 +22346,8 @@
       </c>
       <c r="B1424" s="1" t="inlineStr">
         <is>
-          <t>I tried to act normal too and steered the conversation
-toward an everyday topic.</t>
+          <t>I tried to act normal too and steered the
+conversation toward an everyday topic.</t>
         </is>
       </c>
       <c r="C1424" t="n">
@@ -22539,8 +22560,8 @@
       </c>
       <c r="B1438" s="1" t="inlineStr">
         <is>
-          <t>「What? If there's something you want to eat, just tell
-me.」</t>
+          <t>「What? If there's something you want to eat, just
+tell me.」</t>
         </is>
       </c>
       <c r="C1438" t="n">
@@ -22570,8 +22591,8 @@
       </c>
       <c r="B1440" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes... then, could you make an Okosama lunch (Kids'
-meal) for me？」</t>
+          <t>「Y-yes... then, could you make an Okosama lunch
+(Kids' meal) for me？」</t>
         </is>
       </c>
       <c r="C1440" t="n">
@@ -23096,8 +23117,8 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>「All right...！ Tonight I’ll make an Okosama lunch with
-Rurichiyo-chan’s favorite side dishes！？」</t>
+          <t>「All right...！ Tonight I’ll make an Okosama lunch
+with Rurichiyo-chan’s favorite side dishes！？」</t>
         </is>
       </c>
       <c r="C1474" t="n">
@@ -23522,8 +23543,8 @@
       </c>
       <c r="B1502" s="1" t="inlineStr">
         <is>
-          <t>She looks a bit more mature than the others, but she’s
-still a little girl after all...！</t>
+          <t>She looks a bit more mature than the others, but
+she’s still a little girl after all...！</t>
         </is>
       </c>
       <c r="C1502" t="n">
@@ -24401,7 +24422,8 @@
       </c>
       <c r="B1559" s="1" t="inlineStr">
         <is>
-          <t>Right. Rurichiyo-chan enjoys doing motherly things...！</t>
+          <t>Right. Rurichiyo-chan enjoys doing motherly
+things...！</t>
         </is>
       </c>
       <c r="C1559" t="n">
@@ -24570,7 +24592,8 @@
       </c>
       <c r="B1570" s="1" t="inlineStr">
         <is>
-          <t>「Oh my, you shouldn't move around too much, you know？」</t>
+          <t>「Oh my, you shouldn't move around too much, you
+know？」</t>
         </is>
       </c>
       <c r="C1570" t="n">
@@ -24585,8 +24608,8 @@
       </c>
       <c r="B1571" s="1" t="inlineStr">
         <is>
-          <t>I gently bobbed my head as if enjoying the feel of her
-lap, and Rurichiyo-chan held my head down.</t>
+          <t>I gently bobbed my head as if enjoying the feel of
+her lap, and Rurichiyo-chan held my head down.</t>
         </is>
       </c>
       <c r="C1571" t="n">
@@ -25304,8 +25327,8 @@
       </c>
       <c r="B1618" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... but it's because Rurichiyo-chan's lap feels so
-good...！」</t>
+          <t>「Mmm... but it's because Rurichiyo-chan's lap feels
+so good...！」</t>
         </is>
       </c>
       <c r="C1618" t="n">
@@ -25534,8 +25557,8 @@
       </c>
       <c r="B1633" s="1" t="inlineStr">
         <is>
-          <t>「Oh？ Your nose just twitched, you know？ Could it be...
-you're thinking naughty thoughts？」</t>
+          <t>「Oh？ Your nose just twitched, you know？ Could it
+be... you're thinking naughty thoughts？」</t>
         </is>
       </c>
       <c r="C1633" t="n">
@@ -25580,8 +25603,8 @@
       </c>
       <c r="B1636" s="1" t="inlineStr">
         <is>
-          <t>Being a bit distracted didn't help, and I was slightly
-taken aback.</t>
+          <t>Being a bit distracted didn't help, and I was
+slightly taken aback.</t>
         </is>
       </c>
       <c r="C1636" t="n">
@@ -25841,8 +25864,8 @@
       </c>
       <c r="B1653" s="1" t="inlineStr">
         <is>
-          <t>Her gentle words put me at ease, and I close my eyes a
-little hesitantly.</t>
+          <t>Her gentle words put me at ease, and I close my eyes
+a little hesitantly.</t>
         </is>
       </c>
       <c r="C1653" t="n">
@@ -25857,8 +25880,8 @@
       </c>
       <c r="B1654" s="1" t="inlineStr">
         <is>
-          <t>I'm not planning to actually sleep, but to fully savor
-this moment, it's better to keep my eyes shut.</t>
+          <t>I'm not planning to actually sleep, but to fully
+savor this moment, it's better to keep my eyes shut.</t>
         </is>
       </c>
       <c r="C1654" t="n">
@@ -26043,8 +26066,8 @@
       </c>
       <c r="B1666" s="1" t="inlineStr">
         <is>
-          <t>Knowing Rurichiyo-chan, she might just keep giving the
-lap pillow without waking me.</t>
+          <t>Knowing Rurichiyo-chan, she might just keep giving
+the lap pillow without waking me.</t>
         </is>
       </c>
       <c r="C1666" t="n">
@@ -26137,8 +26160,8 @@
       </c>
       <c r="B1672" s="1" t="inlineStr">
         <is>
-          <t>I open my eyes just a slit, still feeling neither here
-nor there.</t>
+          <t>I open my eyes just a slit, still feeling neither
+here nor there.</t>
         </is>
       </c>
       <c r="C1672" t="n">
@@ -26335,8 +26358,8 @@
       </c>
       <c r="B1685" s="1" t="inlineStr">
         <is>
-          <t>「Um... about what you said, that Oji-sama would end up
-a criminal...」</t>
+          <t>「Um... about what you said, that Oji-sama would end
+up a criminal...」</t>
         </is>
       </c>
       <c r="C1685" t="n">
@@ -26507,7 +26530,8 @@
       </c>
       <c r="B1696" s="1" t="inlineStr">
         <is>
-          <t>Convinced of that, I wait intently for her next words.</t>
+          <t>Convinced of that, I wait intently for her next
+words.</t>
         </is>
       </c>
       <c r="C1696" t="n">
@@ -26932,9 +26956,9 @@
       </c>
       <c r="B1724" s="1" t="inlineStr">
         <is>
-          <t>Liking me as a girl and not having sex, and not having
-sex because we’re uncle and niece, both end up—on the
-surface—as 'not having sex.'</t>
+          <t>Liking me as a girl and not having sex, and not
+having sex because we’re uncle and niece, both end
+up—on the surface—as 'not having sex.'</t>
         </is>
       </c>
       <c r="C1724" t="n">
@@ -26979,7 +27003,8 @@
       </c>
       <c r="B1727" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan, that’s a little different, you know？」</t>
+          <t>「Rurichiyo-chan, that’s a little different, you
+know？」</t>
         </is>
       </c>
       <c r="C1727" t="n">
@@ -27146,8 +27171,8 @@
       </c>
       <c r="B1738" s="1" t="inlineStr">
         <is>
-          <t>「When you have sex, it's something you do after you've
-genuinely fallen for each other...」</t>
+          <t>「When you have sex, it's something you do after
+you've genuinely fallen for each other...」</t>
         </is>
       </c>
       <c r="C1738" t="n">
@@ -27162,8 +27187,8 @@
       </c>
       <c r="B1739" s="1" t="inlineStr">
         <is>
-          <t>Being stared at so intently by Rurichiyo-chan makes me
-embarrassed while I'm speaking.</t>
+          <t>Being stared at so intently by Rurichiyo-chan makes
+me embarrassed while I'm speaking.</t>
         </is>
       </c>
       <c r="C1739" t="n">
@@ -27452,7 +27477,8 @@
       <c r="B1758" s="1" t="inlineStr">
         <is>
           <t>I have no words that could turn our relationship
-upside down, so I grit my teeth behind my closed lips.</t>
+upside down, so I grit my teeth behind my closed
+lips.</t>
         </is>
       </c>
       <c r="C1758" t="n">
@@ -27665,8 +27691,8 @@
       <c r="B1772" s="1" t="inlineStr">
         <is>
           <t>I hadn't really steeled myself until the moment we
-were about to go home, but even so this feels a little
-too soon.</t>
+were about to go home, but even so this feels a
+little too soon.</t>
         </is>
       </c>
       <c r="C1772" t="n">
@@ -27681,8 +27707,8 @@
       </c>
       <c r="B1773" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan liked me... I felt the strength of that
-feeling, and it made me even happier.</t>
+          <t>Rurichiyo-chan liked me... I felt the strength of
+that feeling, and it made me even happier.</t>
         </is>
       </c>
       <c r="C1773" t="n">
@@ -28126,8 +28152,8 @@
       </c>
       <c r="B1802" s="1" t="inlineStr">
         <is>
-          <t>Like me, Rurichiyo-chan must still feel like she can't
-quite believe it.</t>
+          <t>Like me, Rurichiyo-chan must still feel like she
+can't quite believe it.</t>
         </is>
       </c>
       <c r="C1802" t="n">
@@ -28173,7 +28199,8 @@
       <c r="B1805" s="1" t="inlineStr">
         <is>
           <t>Even if I'm not very verbal, Rurichiyo-chan can
-usually read the mood, but right now words are needed.</t>
+usually read the mood, but right now words are
+needed.</t>
         </is>
       </c>
       <c r="C1805" t="n">
@@ -28279,8 +28306,8 @@
       </c>
       <c r="B1812" s="1" t="inlineStr">
         <is>
-          <t>Words over mood... but actions over words — having the
-act will make us believe each other's feelings.</t>
+          <t>Words over mood... but actions over words — having
+the act will make us believe each other's feelings.</t>
         </is>
       </c>
       <c r="C1812" t="n">
@@ -28464,8 +28491,8 @@
       </c>
       <c r="B1824" s="1" t="inlineStr">
         <is>
-          <t>「I'll try harder this time, so Rurichiyo-chan, please,
-okay？」</t>
+          <t>「I'll try harder this time, so Rurichiyo-chan,
+please, okay？」</t>
         </is>
       </c>
       <c r="C1824" t="n">
@@ -28880,7 +28907,8 @@
       <c r="B1851" s="1" t="inlineStr">
         <is>
           <t>When I spoke to calm my racing feelings,
-Rurichiyo-chan's between-her-legs area twitched tight.</t>
+Rurichiyo-chan's between-her-legs area twitched
+tight.</t>
         </is>
       </c>
       <c r="C1851" t="n">
@@ -29232,8 +29260,8 @@
       </c>
       <c r="B1874" s="1" t="inlineStr">
         <is>
-          <t>「Hah, y-yes… something hot and big is inside my belly…
-uk, nh… nfuuhhh…！」</t>
+          <t>「Hah, y-yes… something hot and big is inside my
+belly… uk, nh… nfuuhhh…！」</t>
         </is>
       </c>
       <c r="C1874" t="n">
@@ -29326,8 +29354,8 @@
       </c>
       <c r="B1880" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes... but it's okay, really...？ It doesn't hurt as
-much as I thought from what I saw in manga...」</t>
+          <t>「Y-yes... but it's okay, really...？ It doesn't hurt
+as much as I thought from what I saw in manga...」</t>
         </is>
       </c>
       <c r="C1880" t="n">
@@ -29372,9 +29400,9 @@
       </c>
       <c r="B1883" s="1" t="inlineStr">
         <is>
-          <t>I was surprised — and also happy — that Rurichiyo-chan
-had actually been thinking about real sex for some
-time.</t>
+          <t>I was surprised — and also happy — that
+Rurichiyo-chan had actually been thinking about real
+sex for some time.</t>
         </is>
       </c>
       <c r="C1883" t="n">
@@ -29524,8 +29552,8 @@
       </c>
       <c r="B1893" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan let out a muffled shriek as her vaginal
-walls gave a tight, squeezing clench.</t>
+          <t>Rurichiyo-chan let out a muffled shriek as her
+vaginal walls gave a tight, squeezing clench.</t>
         </is>
       </c>
       <c r="C1893" t="n">
@@ -29634,8 +29662,8 @@
       <c r="B1900" s="1" t="inlineStr">
         <is>
           <t>Since it's her first time having the inside of her
-pussy rubbed like this, maybe she was just startled by
-the unfamiliar sensation？</t>
+pussy rubbed like this, maybe she was just startled
+by the unfamiliar sensation？</t>
         </is>
       </c>
       <c r="C1900" t="n">
@@ -29665,7 +29693,8 @@
       </c>
       <c r="B1902" s="1" t="inlineStr">
         <is>
-          <t>「Then, shall we take a moment and get you used to it？」</t>
+          <t>「Then, shall we take a moment and get you used to
+it？」</t>
         </is>
       </c>
       <c r="C1902" t="n">
@@ -29756,9 +29785,9 @@
       </c>
       <c r="B1908" s="1" t="inlineStr">
         <is>
-          <t>……the inside of her vagina feeling the tip of my penis
-is warm and slippery, with a squeezing, pressurized
-sensation.</t>
+          <t>……the inside of her vagina feeling the tip of my
+penis is warm and slippery, with a squeezing,
+pressurized sensation.</t>
         </is>
       </c>
       <c r="C1908" t="n">
@@ -29773,8 +29802,8 @@
       </c>
       <c r="B1909" s="1" t="inlineStr">
         <is>
-          <t>It's tight, but it feels like she's gently wrapping me
-up, and I can't help but go into a daze.</t>
+          <t>It's tight, but it feels like she's gently wrapping
+me up, and I can't help but go into a daze.</t>
         </is>
       </c>
       <c r="C1909" t="n">
@@ -30448,8 +30477,8 @@
       </c>
       <c r="B1953" s="1" t="inlineStr">
         <is>
-          <t>「Wow... Rurichiyo-chan's love juice is already seeping
-out.」</t>
+          <t>「Wow... Rurichiyo-chan's love juice is already
+seeping out.」</t>
         </is>
       </c>
       <c r="C1953" t="n">
@@ -30509,8 +30538,8 @@
       </c>
       <c r="B1957" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. Like your belly's so happy it's leaking—naughty
-little juice, maybe？」</t>
+          <t>「Yeah. Like your belly's so happy it's
+leaking—naughty little juice, maybe？」</t>
         </is>
       </c>
       <c r="C1957" t="n">
@@ -30632,7 +30661,8 @@
       <c r="B1965" s="1" t="inlineStr">
         <is>
           <t>「If lots of love juices come out, you'll be better at
-sex, and that's important for becoming a mother too…！」</t>
+sex, and that's important for becoming a mother
+too…！」</t>
         </is>
       </c>
       <c r="C1965" t="n">
@@ -31419,8 +31449,8 @@
       </c>
       <c r="B2016" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh—ah, haa...！  It's amazing... Oji-sama's big one
-is all the way up inside my stomach...！」</t>
+          <t>「Nnngh—ah, haa...！  It's amazing... Oji-sama's big
+one is all the way up inside my stomach...！」</t>
         </is>
       </c>
       <c r="C2016" t="n">
@@ -31513,8 +31543,8 @@
       <c r="B2022" s="1" t="inlineStr">
         <is>
           <t>The entrance was plump, but from about midway in the
-vaginal canal it gets narrow and it squeezes me really
-tight.</t>
+vaginal canal it gets narrow and it squeezes me
+really tight.</t>
         </is>
       </c>
       <c r="C2022" t="n">
@@ -31881,7 +31911,8 @@
       <c r="B2046" s="1" t="inlineStr">
         <is>
           <t>I give little, quick jostles so it's not too much;
-just that and Rurichiyo-chan starts getting worked up.</t>
+just that and Rurichiyo-chan starts getting worked
+up.</t>
         </is>
       </c>
       <c r="C2046" t="n">
@@ -32328,8 +32359,8 @@
       </c>
       <c r="B2075" s="1" t="inlineStr">
         <is>
-          <t>When I can tell where Rurichiyo is feeling it, I get a
-little more composed.</t>
+          <t>When I can tell where Rurichiyo is feeling it, I get
+a little more composed.</t>
         </is>
       </c>
       <c r="C2075" t="n">
@@ -32788,8 +32819,8 @@
       </c>
       <c r="B2105" s="1" t="inlineStr">
         <is>
-          <t>The sliding's gotten a lot better, and I can tell from
-Rurichiyo-chan's voice that the pain's easing.</t>
+          <t>The sliding's gotten a lot better, and I can tell
+from Rurichiyo-chan's voice that the pain's easing.</t>
         </is>
       </c>
       <c r="C2105" t="n">
@@ -33216,8 +33247,8 @@
       </c>
       <c r="B2133" s="1" t="inlineStr">
         <is>
-          <t>「Haa, haa, haa... please... Oji-sama, please feel good
-too...！」</t>
+          <t>「Haa, haa, haa... please... Oji-sama, please feel
+good too...！」</t>
         </is>
       </c>
       <c r="C2133" t="n">
@@ -33780,8 +33811,8 @@
       <c r="B2170" s="1" t="inlineStr">
         <is>
           <t>Having come to climax inside Rurichiyo-chan, I was
-intoxicated by the impulse of semen rushing through my
-penis…</t>
+intoxicated by the impulse of semen rushing through
+my penis…</t>
         </is>
       </c>
       <c r="C2170" t="n">
@@ -34484,7 +34515,8 @@
       </c>
       <c r="B2216" s="1" t="inlineStr">
         <is>
-          <t>I said that and kissed Rurichiyo-chan on the forehead.</t>
+          <t>I said that and kissed Rurichiyo-chan on the
+forehead.</t>
         </is>
       </c>
       <c r="C2216" t="n">

--- a/processed_ruby_restored_xlsx/sc122_瑠璃千代２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc122_瑠璃千代２：恋人化.ss.xlsx
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>「Not really... it's not like that...？」</t>
+          <t>Not really... it's not like that...？</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>「No... really, I'm fine...」</t>
+          <t>No... really, I'm fine...</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>「I, too, know Oji-sama very well... yes, I know me
+          <t>「I, too, know Oji-sama very well... yes, I know him
 extremely well...！」</t>
         </is>
       </c>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>Does this mean she wants me to leave...?</t>
+          <t>Does this mean she wants me to leave...?"</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>「No, no — making you happy is what makes me happy.」</t>
+          <t>No, no — making you happy is what makes me happy.</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... You're noisy.」</t>
+          <t>Ugh... You're noisy.</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>「Oh… really, great-grandma… you…」</t>
+          <t>Oh… really, great-grandma… you…</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>...Have they figured out I'm a virgin！？</t>
+          <t>...Have they figured out I'm a virgin！？"</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>I'm a real old hand who's seen it all...no charm at
+          <t>He's a real old hand who's seen it all...no charm at
 all.</t>
         </is>
       </c>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>「Um… um… Great-aunt…？」</t>
+          <t>Um… um… Great-aunt…？</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -6166,8 +6166,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>「Well, the truth is, me and the old man had a bit of
-lovin' right here...」</t>
+          <t>Well, the truth is, me and the old man had a bit of
+lovin' right here...</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -7244,7 +7244,7 @@
       <c r="B442" s="1" t="inlineStr">
         <is>
           <t>「Because Rurichiyo says about Hajime, 'shuki shuki
-shuki da~i shuki'」</t>
+shuki da~i shuki'"</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>"'</t>
+          <t>"」</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7459,8 +7459,8 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo doesn't say anything, but I can get the
-gist from her voice and the way she speaks…」</t>
+          <t>Rurichiyo doesn」t say anything, but I can get the
+gist from her voice and the way she speaks…</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -7597,9 +7597,8 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>「No — I'm not just any old broad！ I'm an old broad
-who loves Rurichiyo deeply, deeeply！ Just an old
-broad！」</t>
+          <t>No — I'm not just any old broad！ I'm an old broad who
+loves Rurichiyo deeply, deeeply！ Just an old broad！</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7720,7 +7719,7 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t>I can't give shape to my will toward her, and I trail
+          <t>I can't give shape to my will toward she, and I trail
 off in vain.</t>
         </is>
       </c>
@@ -8417,7 +8416,7 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>When I got to the washroom, I stumbled toward
+          <t>When he got to the washroom, he stumbled toward
 everyone's laundry.</t>
         </is>
       </c>
@@ -8463,7 +8462,7 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>I crouched there and muttered to myself.</t>
+          <t>He crouched there and muttered to himself.</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8556,7 +8555,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Suu~ haa~ suu~ haa~...！」</t>
+          <t>Suu~ haa~ suu~ haa~...！</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -9369,8 +9368,8 @@
       </c>
       <c r="B580" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama. I won't be angry, so please tell me
-plainly...！」</t>
+          <t>Oji-sama. I won't be angry, so please tell me
+plainly...！</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -9417,8 +9416,8 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>「Ah, um... I was sniffing Rurichiyo-chan's panties...
-I'm sorry.」</t>
+          <t>Ah, um... I was sniffing Rurichiyo-chan's panties...
+I'm sorry.</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9448,7 +9447,7 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>「Ah...！」</t>
+          <t>Ah...！</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -9463,7 +9462,7 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>When I gave up and apologized honestly,
+          <t>When he gave up and apologized honestly,
 Rurichiyo-chan covered her mouth with her hand and
 collapsed.</t>
         </is>
@@ -9495,7 +9494,7 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>「...So that's how it was, Oji-sama？」</t>
+          <t>...So that's how it was, Oji-sama？</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -9525,7 +9524,7 @@
       </c>
       <c r="B590" s="1" t="inlineStr">
         <is>
-          <t>「Yes? ...'So'? What do you mean?」</t>
+          <t>Yes? ...'So'? What do you mean?</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -10167,7 +10166,7 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>「She said if I was sniffing panties, be careful...
+          <t>「She said if he was sniffing panties, be careful...
 Great-aunt said that...」</t>
         </is>
       </c>
@@ -11382,7 +11381,7 @@
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>Hajime</t>
+          <t>Hajime":""Wha—"</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -11718,7 +11717,7 @@
       </c>
       <c r="B733" s="1" t="inlineStr">
         <is>
-          <t>I demanded she strip as soon as we got to the room.</t>
+          <t>He demanded she strip as soon as we got to the room.</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -11857,8 +11856,8 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>You can tell she’s not completely over it, but even
-so she takes off her clothes one by one and ends up
+          <t>You can tell they’re not completely over it, but even
+so they take off their clothes one by one and end up
 completely naked.</t>
         </is>
       </c>
@@ -11949,8 +11948,8 @@
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t>Seeing that my penis was erect, Rurichiyo-chan gave a
-small cry.</t>
+          <t>Seeing that his penis was erect, Rurichiyo-chan gave
+a small cry.</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -11965,8 +11964,8 @@
       </c>
       <c r="B749" s="1" t="inlineStr">
         <is>
-          <t>I'd decided in my heart to stop partway, but there
-was naked Rurichiyo-chan right in front of me.</t>
+          <t>He'd decided in his heart to stop partway, but there
+was naked Rurichiyo-chan right in front of him.</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -11981,8 +11980,8 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>Besides, even I was starting to get into it a little,
-partly as an act.</t>
+          <t>Besides, even he was starting to get into it a
+little, partly as an act.</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -12088,7 +12087,7 @@
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
-          <t>Then I placed my penis against the area between her
+          <t>Then he placed his penis against the area between her
 legs.</t>
         </is>
       </c>
@@ -13252,8 +13251,8 @@
       </c>
       <c r="B833" s="1" t="inlineStr">
         <is>
-          <t>Surprised by an action of mine she never saw coming,
-has she cooled off even a little？</t>
+          <t>Surprised by an action of mine they never saw coming,
+have they cooled off even a little？</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -14038,8 +14037,7 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>「Pardon？ Passion isn't something to be
-suppressed...？」</t>
+          <t>Pardon？ Passion isn」t something to be suppressed...？</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -14163,7 +14161,7 @@
       </c>
       <c r="B892" s="1" t="inlineStr">
         <is>
-          <t>Or rather, was I embarrassed？</t>
+          <t>Or rather, was he embarrassed？</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -14253,8 +14251,8 @@
       </c>
       <c r="B898" s="1" t="inlineStr">
         <is>
-          <t>It was like that earlier too, but when she sulks and
-then cools down a bit I think it actually ends up
+          <t>It was like that earlier too, but when they sulk and
+then cool down a bit I think it actually ends up
 being a good thing.</t>
         </is>
       </c>
@@ -14605,7 +14603,7 @@
       </c>
       <c r="B921" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！　...！」</t>
+          <t>Smooch！　...！</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -14912,8 +14910,8 @@
       </c>
       <c r="B941" s="1" t="inlineStr">
         <is>
-          <t>「Okay... smooch, smoo, smooch, smooch！ Nn... smooch！
-Smooch！ Smooch！」</t>
+          <t>Okay... smooch, smoo, smooch, smooch！ Nn... smooch！
+Smooch！ Smooch！</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -15299,7 +15297,7 @@
       </c>
       <c r="B966" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -15359,7 +15357,7 @@
       </c>
       <c r="B970" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -15621,7 +15619,7 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>I let out a big sigh, pleased to see Rurichiyo-chan
+          <t>He let out a big sigh, pleased to see Rurichiyo-chan
 getting more and more excited.</t>
         </is>
       </c>
@@ -15683,7 +15681,7 @@
       </c>
       <c r="B991" s="1" t="inlineStr">
         <is>
-          <t>「Nfuuhhh...？！」</t>
+          <t>「Nfuuhhh...？！</t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -16347,7 +16345,7 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>The realization that I'm making me feel good is
+          <t>The realization that I'm making him feel good is
 egging Rurichiyo-chan on……。</t>
         </is>
       </c>
@@ -17396,8 +17394,8 @@
       </c>
       <c r="B1102" s="1" t="inlineStr">
         <is>
-          <t>Despite my words, I writhed my body as if to say it
-was more of a reward.</t>
+          <t>Despite his words, he writhed his body as if to say
+it was more of a reward.</t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -17474,7 +17472,7 @@
       <c r="B1107" s="1" t="inlineStr">
         <is>
           <t>Even while being scolded by Rurichiyo-chan, being
-kissed made me genuinely relieved.</t>
+kissed made him genuinely relieved.</t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -17489,8 +17487,8 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>It was a strange feeling, but if I indulged in being
-doted on, no contradiction rose in my heart.</t>
+          <t>It was a strange feeling, but if he indulged in being
+doted on, no contradiction rose in his heart.</t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -18951,7 +18949,7 @@
       </c>
       <c r="B1203" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -19011,7 +19009,7 @@
       </c>
       <c r="B1207" s="1" t="inlineStr">
         <is>
-          <t>But if I'm serious, she can't afford to worry about
+          <t>But if he's serious, she can't afford to worry about
 that.</t>
         </is>
       </c>
@@ -19363,8 +19361,8 @@
       </c>
       <c r="B1230" s="1" t="inlineStr">
         <is>
-          <t>While not denying my own words, I put up a defensive
-line.</t>
+          <t>While not denying his own words, he put up a
+defensive line.</t>
         </is>
       </c>
       <c r="C1230" t="n">
@@ -20452,8 +20450,8 @@
       </c>
       <c r="B1301" s="1" t="inlineStr">
         <is>
-          <t>「Well, I... don't have a ticket, so I'll get off the
-ship, okay...？」</t>
+          <t>Well, I... don't have a ticket, so I'll get off the
+ship, okay...？</t>
         </is>
       </c>
       <c r="C1301" t="n">
@@ -21675,7 +21673,7 @@
       </c>
       <c r="B1380" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1380" t="n">
@@ -21782,7 +21780,7 @@
       </c>
       <c r="B1387" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1387" t="n">
@@ -21859,7 +21857,7 @@
       </c>
       <c r="B1392" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1392" t="n">
@@ -21936,7 +21934,7 @@
       </c>
       <c r="B1397" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1397" t="n">
@@ -22041,7 +22039,7 @@
       </c>
       <c r="B1404" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1404" t="n">
@@ -23133,7 +23131,7 @@
       </c>
       <c r="B1475" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1475" t="n">
@@ -23210,7 +23208,7 @@
       </c>
       <c r="B1480" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1480" t="n">
@@ -23286,7 +23284,7 @@
       </c>
       <c r="B1485" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1485" t="n">
@@ -23346,7 +23344,7 @@
       </c>
       <c r="B1489" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1489" t="n">
@@ -23483,7 +23481,7 @@
       </c>
       <c r="B1498" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1498" t="n">
@@ -23652,8 +23650,8 @@
       </c>
       <c r="B1509" s="1" t="inlineStr">
         <is>
-          <t>I beckon to Rurichiyo-chan peeking from the shadow of
-the door.</t>
+          <t>He beckons to Rurichiyo-chan peeking from the shadow
+of the door.</t>
         </is>
       </c>
       <c r="C1509" t="n">
@@ -23991,7 +23989,7 @@
       </c>
       <c r="B1531" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1531" t="n">
@@ -24961,7 +24959,7 @@
       </c>
       <c r="B1594" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C1594" t="n">
@@ -25358,7 +25356,7 @@
       </c>
       <c r="B1620" s="1" t="inlineStr">
         <is>
-          <t>「Okay, okay... I get it...！」</t>
+          <t>Okay, okay... I get it...！</t>
         </is>
       </c>
       <c r="C1620" t="n">
@@ -26268,7 +26266,7 @@
       </c>
       <c r="B1679" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C1679" t="n">
@@ -26651,7 +26649,7 @@
       </c>
       <c r="B1704" s="1" t="inlineStr">
         <is>
-          <t>「…When Oji-sama said I liked me as a girl, you also
+          <t>「…When Oji-sama said he liked me as a girl, you also
 said you wanted to cherish me, didn’t you？」</t>
         </is>
       </c>
@@ -27279,7 +27277,7 @@
       </c>
       <c r="B1745" s="1" t="inlineStr">
         <is>
-          <t>Hmm, was that a bit too honest just now...？</t>
+          <t>Hmm, was that a bit too honest just now...？"</t>
         </is>
       </c>
       <c r="C1745" t="n">
@@ -29092,8 +29090,8 @@
       </c>
       <c r="B1863" s="1" t="inlineStr">
         <is>
-          <t>Waiting for Rurichiyo-chan's response, I slowly push
-my penis in.</t>
+          <t>Waiting for Rurichiyo-chan's response, he slowly
+pushes his penis in.</t>
         </is>
       </c>
       <c r="C1863" t="n">
@@ -29154,7 +29152,7 @@
       <c r="B1867" s="1" t="inlineStr">
         <is>
           <t>…Completely different from before, her pussy gently
-receives my penis.</t>
+receives his penis.</t>
         </is>
       </c>
       <c r="C1867" t="n">
@@ -29785,7 +29783,7 @@
       </c>
       <c r="B1908" s="1" t="inlineStr">
         <is>
-          <t>……the inside of her vagina feeling the tip of my
+          <t>……the inside of her vagina feeling the tip of his
 penis is warm and slippery, with a squeezing,
 pressurized sensation.</t>
         </is>
@@ -31064,8 +31062,8 @@
       </c>
       <c r="B1991" s="1" t="inlineStr">
         <is>
-          <t>A piercing scream rose, and at the same time I felt a
-sudden, snapping sensation in my penis.</t>
+          <t>A piercing scream rose, and at the same time he felt
+a sudden, snapping sensation in his penis.</t>
         </is>
       </c>
       <c r="C1991" t="n">
@@ -31156,7 +31154,7 @@
       </c>
       <c r="B1997" s="1" t="inlineStr">
         <is>
-          <t>Thinking it might be so, I looked down and saw blood
+          <t>Thinking it might be so, he looked down and saw blood
 flowing from the junction.</t>
         </is>
       </c>
@@ -31172,7 +31170,7 @@
       </c>
       <c r="B1998" s="1" t="inlineStr">
         <is>
-          <t>Even though I'd taken her first, I felt a sense of
+          <t>Even though he'd taken her first, he felt a sense of
 romance and suddenly became really happy...！</t>
         </is>
       </c>
@@ -31249,7 +31247,7 @@
       </c>
       <c r="B2003" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan picks up the murmured words I
+          <t>Rurichiyo-chan picks up the murmured words he
 accidentally let slip.</t>
         </is>
       </c>
@@ -31341,7 +31339,7 @@
       </c>
       <c r="B2009" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C2009" t="n">
@@ -31449,8 +31447,8 @@
       </c>
       <c r="B2016" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh—ah, haa...！  It's amazing... Oji-sama's big
-one is all the way up inside my stomach...！」</t>
+          <t>Nnngh—ah, haa...！  It's amazing... Oji-sama's big one
+is all the way up inside my stomach...！</t>
         </is>
       </c>
       <c r="C2016" t="n">
@@ -31496,7 +31494,7 @@
       </c>
       <c r="B2019" s="1" t="inlineStr">
         <is>
-          <t>「Mm... it's really all the way in, isn't it...！」</t>
+          <t>Mm... it's really all the way in, isn't it...！</t>
         </is>
       </c>
       <c r="C2019" t="n">
@@ -31802,7 +31800,7 @@
       </c>
       <c r="B2039" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Ah, aah—！ Amazing！ Uuh, huff, huff！ Nnn—...！」</t>
+          <t>Nn！ Ah, aah—！ Amazing！ Uuh, huff, huff！ Nnn—...！</t>
         </is>
       </c>
       <c r="C2039" t="n">
@@ -31864,7 +31862,7 @@
       </c>
       <c r="B2043" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ahn, nna！ Ah！ Oji-sama！」</t>
+          <t>Nn... ahn, nna！ Ah！ Oji-sama！</t>
         </is>
       </c>
       <c r="C2043" t="n">
@@ -32004,7 +32002,7 @@
       </c>
       <c r="B2052" s="1" t="inlineStr">
         <is>
-          <t>「Pl-please... nn！ Ngh！？」</t>
+          <t>Pl-please... nn！ Ngh！？</t>
         </is>
       </c>
       <c r="C2052" t="n">
@@ -32282,8 +32280,8 @@
       </c>
       <c r="B2070" s="1" t="inlineStr">
         <is>
-          <t>I push my penis in deep and grind so the tip hits the
-back.</t>
+          <t>He pushes his penis in deep and grinds so the tip
+hits the back.</t>
         </is>
       </c>
       <c r="C2070" t="n">
@@ -32405,7 +32403,7 @@
       </c>
       <c r="B2078" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C2078" t="n">
@@ -33003,7 +33001,7 @@
       </c>
       <c r="B2117" s="1" t="inlineStr">
         <is>
-          <t>「U-uh—ahh！  Fah, aaah... ah...！」</t>
+          <t>U-uh—ahh！  Fah, aaah... ah...！</t>
         </is>
       </c>
       <c r="C2117" t="n">
@@ -33369,7 +33367,7 @@
       </c>
       <c r="B2141" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nfuu... Ugh！ Nn！ Fwaa... Ah！ Ah, ah！ Ah！」</t>
+          <t>Nn！ Nfuu... Ugh！ Nn！ Fwaa... Ah！ Ah, ah！ Ah！</t>
         </is>
       </c>
       <c r="C2141" t="n">
@@ -33431,7 +33429,7 @@
       <c r="B2145" s="1" t="inlineStr">
         <is>
           <t>If she gets into it and starts moving her hips,
-pleasure rises up into my penis right away.</t>
+pleasure rises up into her penis right away.</t>
         </is>
       </c>
       <c r="C2145" t="n">
